--- a/naver-place-crawler/results_health/광주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/광주_헬스장.xlsx
@@ -426,8 +426,8 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
-    <col width="48" customWidth="1" min="8" max="8"/>
+    <col width="31" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -628,10 +628,10 @@
         <v>351</v>
       </c>
       <c r="Q2" t="n">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="R2" t="n">
-        <v>2260</v>
+        <v>2261</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -760,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>에스짐 두암점 24시 헬스 PT</t>
+          <t>NS휘트니스 봉선점 해머스트렝스오피셜센터 PT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>sgym6@naver.com</t>
+          <t>nsfitness5@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1487-1017</t>
+          <t>0507-1443-6318</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>광주 동구 밤실로 154 5층 SGYM 두암점</t>
+          <t>광주 남구 봉선2로 49 5층 유산소존 6층 웨이트존</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sgym6/223209262378</t>
+          <t>https://blog.naver.com/nsfitness5</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4c90x</t>
+          <t>https://talk.naver.com/ct/wtveflr</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -817,17 +817,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>745</v>
+        <v>368</v>
       </c>
       <c r="Q4" t="n">
-        <v>1139</v>
+        <v>595</v>
       </c>
       <c r="R4" t="n">
-        <v>1884</v>
+        <v>963</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1223385391</t>
+          <t>1825238671</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1223385391</t>
+          <t>https://m.place.naver.com/place/1825238671</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -853,34 +853,34 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>���스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NS휘트니스 봉선점 해머스트렝스오피셜센터 PT</t>
+          <t>에스짐 두암점 24시 헬스 PT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nsfitness5@naver.com</t>
+          <t>sgym6@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1443-6318</t>
+          <t>0507-1487-1017</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>광주 남구 봉선2로 49 5층 유산소존 6층 웨이트존</t>
+          <t>광주 동구 밤실로 154 5층 SGYM 두암점</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nsfitness5</t>
+          <t>https://blog.naver.com/sgym6/223209262378</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wtveflr</t>
+          <t>https://talk.naver.com/ct/w4c90x</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -915,17 +915,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>368</v>
+        <v>745</v>
       </c>
       <c r="Q5" t="n">
-        <v>596</v>
+        <v>1142</v>
       </c>
       <c r="R5" t="n">
-        <v>964</v>
+        <v>1887</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,12 +934,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1825238671</t>
+          <t>1223385391</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1825238671</t>
+          <t>https://m.place.naver.com/place/1223385391</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -956,29 +956,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>육체미 첨단점</t>
+          <t>NS휘트니스 선운점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>abcshowkr@naver.com</t>
+          <t>nsfitness_seonun@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>062-972-0002</t>
+          <t>0507-1427-7668</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>광주 광산구 첨단중앙로170번길 92 첨단스포츠센터 5층, 육체미</t>
+          <t>광주 광산구 어등대로 555 2동 2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/6eauty6ody__chumdan3</t>
+          <t>https://www.instagram.com/nsfitness_seonun</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -998,10 +998,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wh23ln4</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1013,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>109</v>
+        <v>64</v>
       </c>
       <c r="Q6" t="n">
-        <v>310</v>
+        <v>106</v>
       </c>
       <c r="R6" t="n">
-        <v>419</v>
+        <v>170</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,12 +1032,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1499021085</t>
+          <t>2097553652</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1499021085</t>
+          <t>https://m.place.naver.com/place/2097553652</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1050,30 +1054,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>에스짐24시피트니스 진월점</t>
+          <t>24시 올라운드휘트니스 금호점 헬스 PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>sgym3@naver.com</t>
+          <t>allround_fitness5@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0507-1438-7908</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>광주 남구 서문대로 665 6층 SGYM 진월점</t>
+          <t>광주 서구 운천로 23-1 2~3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sgym3/223208188125</t>
+          <t>https://allroundfitness.kr</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1093,12 +1101,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4620r</t>
+          <t>https://talk.naver.com/ct/wkdxhjp</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1107,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>413</v>
+        <v>262</v>
       </c>
       <c r="Q7" t="n">
-        <v>400</v>
+        <v>622</v>
       </c>
       <c r="R7" t="n">
-        <v>813</v>
+        <v>884</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1122,12 +1130,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1264832152</t>
+          <t>1709345373</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1264832152</t>
+          <t>https://m.place.naver.com/place/1709345373</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1144,34 +1152,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>에스짐24시 풍암점</t>
+          <t>24시 올라운드 휘트니스 운암점 헬스 PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>sgympa@naver.com</t>
+          <t>allround_fitness@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1330-6135</t>
+          <t>0507-1461-2096</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>광주 서구 송풍로17번길 9 2층</t>
+          <t>광주 북구 북문대로 184 2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sgym.pa</t>
+          <t>http://pf.kakao.com/_GRzxen/chat</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1191,12 +1199,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wpu0gc2</t>
+          <t>https://talk.naver.com/ct/we94hjj</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1205,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>30</v>
+        <v>516</v>
       </c>
       <c r="Q8" t="n">
-        <v>21</v>
+        <v>286</v>
       </c>
       <c r="R8" t="n">
-        <v>51</v>
+        <v>802</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2093843033</t>
+          <t>1509126970</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2093843033</t>
+          <t>https://m.place.naver.com/place/1509126970</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1237,39 +1245,35 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>24시 올라운드휘트니스 금호점 헬스 PT</t>
+          <t>레벨업피트니스 헬스&amp;PT 첨단점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>allround_fitness5@naver.com</t>
+          <t>wjddbqls0383@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0507-1438-7908</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>광주 서구 운천로 23-1 2~3층</t>
+          <t>광주 광산구 첨단중앙로124번길 79 2층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://allroundfitness.kr</t>
+          <t>https://blog.naver.com/wjddbqls0383</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1284,17 +1288,13 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wkdxhjp</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1303,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>262</v>
+        <v>732</v>
       </c>
       <c r="Q9" t="n">
-        <v>620</v>
+        <v>1076</v>
       </c>
       <c r="R9" t="n">
-        <v>882</v>
+        <v>1808</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1709345373</t>
+          <t>1078877238</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1709345373</t>
+          <t>https://m.place.naver.com/place/1078877238</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1340,34 +1340,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>24시 올라운드 휘트니스 운암점 헬스 PT</t>
+          <t>나우휘트니스 헬스&amp;PT 봉선점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>allround_fitness@naver.com</t>
+          <t>nowfitness_1@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1461-2096</t>
+          <t>0507-1487-8892</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>광주 북구 북문대로 184 2층</t>
+          <t>광주 남구 봉선2로 41 스카이빌딩 3층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_GRzxen/chat</t>
+          <t>https://blog.naver.com/nowfitness_1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/we94hjj</t>
+          <t>https://talk.naver.com/ct/w41axl</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1401,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="Q10" t="n">
-        <v>285</v>
+        <v>251</v>
       </c>
       <c r="R10" t="n">
-        <v>801</v>
+        <v>766</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1509126970</t>
+          <t>1006368175</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1509126970</t>
+          <t>https://m.place.naver.com/place/1006368175</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1502,10 +1502,10 @@
         <v>271</v>
       </c>
       <c r="Q11" t="n">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="R11" t="n">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_health/광주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/광주_헬스장.xlsx
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>글램핏 상무점 24시 헬스 PT</t>
+          <t>넥스트짐 광주 태전동점 헬스 PT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>glamfit23@naver.com</t>
+          <t>nextgym07@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1348-6107</t>
+          <t>0507-1371-0124</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>광주 서구 상무중앙로 34 4층</t>
+          <t>경기 광주시 태봉로 116-18</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/glamfit23</t>
+          <t>https://blog.naver.com/nextgym07</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w42a3f</t>
+          <t>https://talk.naver.com/ct/wv39ze2</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>351</v>
+        <v>729</v>
       </c>
       <c r="Q2" t="n">
-        <v>1910</v>
+        <v>941</v>
       </c>
       <c r="R2" t="n">
-        <v>2261</v>
+        <v>1670</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1034250827</t>
+          <t>1303499041</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1034250827</t>
+          <t>https://m.place.naver.com/place/1303499041</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -662,34 +662,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NS휘트니스 진월점 헬스장 PT</t>
+          <t>에스짐 헬스PT 용봉점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nsfitness3@naver.com</t>
+          <t>sgym14@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1393-8667</t>
+          <t>0507-1429-1696</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>광주 남구 서문대로 700 3층</t>
+          <t>광주 북구 비엔날레로 80 7층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://nsfitness.imweb.me</t>
+          <t>https://blog.naver.com/sgym14/223917864659</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w46fuy</t>
+          <t>https://talk.naver.com/ct/wejy33f</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>720</v>
+        <v>643</v>
       </c>
       <c r="Q3" t="n">
-        <v>1316</v>
+        <v>454</v>
       </c>
       <c r="R3" t="n">
-        <v>2036</v>
+        <v>1097</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +738,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1659855087</t>
+          <t>2056986615</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1659855087</t>
+          <t>https://m.place.naver.com/place/2056986615</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="Q4" t="n">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="R4" t="n">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -846,41 +846,41 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>���스장</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>에스짐 두암점 24시 헬스 PT</t>
+          <t>글램핏 상무점 24시 헬스 PT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>sgym6@naver.com</t>
+          <t>glamfit23@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1487-1017</t>
+          <t>0507-1348-6107</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>광주 동구 밤실로 154 5층 SGYM 두암점</t>
+          <t>광주 서구 상무중앙로 34 4층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sgym6/223209262378</t>
+          <t>https://blog.naver.com/glamfit23</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4c90x</t>
+          <t>https://talk.naver.com/ct/w42a3f</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>745</v>
+        <v>351</v>
       </c>
       <c r="Q5" t="n">
-        <v>1142</v>
+        <v>1964</v>
       </c>
       <c r="R5" t="n">
-        <v>1887</v>
+        <v>2315</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,17 +934,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1223385391</t>
+          <t>1034250827</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1223385391</t>
+          <t>https://m.place.naver.com/place/1034250827</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -956,29 +956,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NS휘트니스 선운점</t>
+          <t>에스짐24시피트니스 진월점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nsfitness_seonun@naver.com</t>
+          <t>sgym3@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0507-1427-7668</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>광주 광산구 어등대로 555 2동 2층</t>
+          <t>광주 남구 서문대로 665 6층 SGYM 진월점</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nsfitness_seonun</t>
+          <t>https://blog.naver.com/sgym3/223208188125</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -993,7 +989,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1003,7 +999,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wh23ln4</t>
+          <t>https://talk.naver.com/ct/w4620r</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>64</v>
+        <v>412</v>
       </c>
       <c r="Q6" t="n">
-        <v>106</v>
+        <v>401</v>
       </c>
       <c r="R6" t="n">
-        <v>170</v>
+        <v>813</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,17 +1028,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2097553652</t>
+          <t>1264832152</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2097553652</t>
+          <t>https://m.place.naver.com/place/1264832152</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1054,29 +1050,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>24시 올라운드휘트니스 금호점 헬스 PT</t>
+          <t>NS휘트니스 선운점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>allround_fitness5@naver.com</t>
+          <t>nsfitness_seonun@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1438-7908</t>
+          <t>0507-1427-7668</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>광주 서구 운천로 23-1 2~3층</t>
+          <t>광주 광산구 어등대로 555 2동 2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://allroundfitness.kr</t>
+          <t>https://www.instagram.com/nsfitness_seonun</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1101,12 +1097,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wkdxhjp</t>
+          <t>https://talk.naver.com/ct/wh23ln4</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1115,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>262</v>
+        <v>73</v>
       </c>
       <c r="Q7" t="n">
-        <v>622</v>
+        <v>116</v>
       </c>
       <c r="R7" t="n">
-        <v>884</v>
+        <v>189</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,17 +1126,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1709345373</t>
+          <t>2097553652</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1709345373</t>
+          <t>https://m.place.naver.com/place/2097553652</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1152,29 +1148,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>24시 올라운드 휘트니스 운암점 헬스 PT</t>
+          <t>24시 올라운드휘트니스 금호점 헬스 PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>allround_fitness@naver.com</t>
+          <t>allround_fitness5@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1461-2096</t>
+          <t>0507-1438-7908</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>광주 북구 북문대로 184 2층</t>
+          <t>광주 서구 운천로 23-1 2~3층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_GRzxen/chat</t>
+          <t>https://allroundfitness.kr</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1189,7 +1185,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1199,7 +1195,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/we94hjj</t>
+          <t>https://talk.naver.com/ct/wkdxhjp</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1213,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>516</v>
+        <v>266</v>
       </c>
       <c r="Q8" t="n">
-        <v>286</v>
+        <v>636</v>
       </c>
       <c r="R8" t="n">
-        <v>802</v>
+        <v>902</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,52 +1224,56 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1509126970</t>
+          <t>1709345373</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1509126970</t>
+          <t>https://m.place.naver.com/place/1709345373</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>레벨업피트니스 헬스&amp;PT 첨단점</t>
+          <t>24시 올라운드 휘트니스 운암점 헬스 PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>wjddbqls0383@naver.com</t>
+          <t>allround_fitness@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0507-1461-2096</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>광주 광산구 첨단중앙로124번길 79 2층</t>
+          <t>광주 북구 북문대로 184 2층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wjddbqls0383</t>
+          <t>http://pf.kakao.com/_GRzxen/chat</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1283,18 +1283,22 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/we94hjj</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1303,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>732</v>
+        <v>520</v>
       </c>
       <c r="Q9" t="n">
-        <v>1076</v>
+        <v>291</v>
       </c>
       <c r="R9" t="n">
-        <v>1808</v>
+        <v>811</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,56 +1322,56 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1078877238</t>
+          <t>1509126970</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1078877238</t>
+          <t>https://m.place.naver.com/place/1509126970</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>나우휘트니스 헬스&amp;PT 봉선점</t>
+          <t>짐플릭스 첨단점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>nowfitness_1@naver.com</t>
+          <t>gymflix@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1487-8892</t>
+          <t>0507-1364-2795</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>광주 남구 봉선2로 41 스카이빌딩 3층</t>
+          <t>광주 광산구 임방울대로800번길 72 3층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nowfitness_1</t>
+          <t>https://www.gymflix.co.kr/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1377,7 +1381,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1387,7 +1391,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w41axl</t>
+          <t>https://talk.naver.com/ct/wkfba0h</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1401,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>515</v>
+        <v>274</v>
       </c>
       <c r="Q10" t="n">
-        <v>251</v>
+        <v>849</v>
       </c>
       <c r="R10" t="n">
-        <v>766</v>
+        <v>1123</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,17 +1420,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1006368175</t>
+          <t>1955578541</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1006368175</t>
+          <t>https://m.place.naver.com/place/1955578541</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1438,7 +1442,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>짐플릭스 첨단점</t>
+          <t>짐플릭스 수완점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1449,13 +1453,13 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1364-2795</t>
+          <t>0507-1383-2795</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>광주 광산구 임방울대로800번길 72 3층</t>
+          <t>광주 광산구 임방울대로 342 8층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1499,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="Q11" t="n">
-        <v>885</v>
+        <v>724</v>
       </c>
       <c r="R11" t="n">
-        <v>1156</v>
+        <v>985</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,17 +1518,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1955578541</t>
+          <t>1999324427</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1955578541</t>
+          <t>https://m.place.naver.com/place/1999324427</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/광주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/광주_헬스장.xlsx
@@ -421,13 +421,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="31" customWidth="1" min="7" max="7"/>
-    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>넥스트짐 광주 태전동점 헬스 PT</t>
+          <t>에스짐 헬스PT 용봉점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nextgym07@naver.com</t>
+          <t>sgym14@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1371-0124</t>
+          <t>0507-1429-1696</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 광주시 태봉로 116-18</t>
+          <t>광주 북구 비엔날레로 80 7층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nextgym07</t>
+          <t>https://blog.naver.com/sgym14/223917864659</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wv39ze2</t>
+          <t>https://talk.naver.com/ct/wejy33f</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>729</v>
+        <v>645</v>
       </c>
       <c r="Q2" t="n">
-        <v>941</v>
+        <v>460</v>
       </c>
       <c r="R2" t="n">
-        <v>1670</v>
+        <v>1105</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1303499041</t>
+          <t>2056986615</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1303499041</t>
+          <t>https://m.place.naver.com/place/2056986615</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -662,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>에스짐 헬스PT 용봉점</t>
+          <t>WE휘트니스 첨단점 헬스 PT 필라테스</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>sgym14@naver.com</t>
+          <t>wefit33@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1429-1696</t>
+          <t>0507-1306-6047</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>광주 북구 비엔날레로 80 7층</t>
+          <t>광주 광산구 임방울대로826번길 29-31 6층 602~608호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sgym14/223917864659</t>
+          <t>https://www.instagram.com/wefit_cheomdan</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -699,19 +699,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wejy33f</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -723,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>643</v>
+        <v>516</v>
       </c>
       <c r="Q3" t="n">
-        <v>454</v>
+        <v>701</v>
       </c>
       <c r="R3" t="n">
-        <v>1097</v>
+        <v>1217</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +734,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2056986615</t>
+          <t>1094731490</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2056986615</t>
+          <t>https://m.place.naver.com/place/1094731490</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -760,34 +756,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NS휘트니스 봉선점 해머스트렝스오피셜센터 PT</t>
+          <t>NS휘트니스 진월점 헬스장 PT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nsfitness5@naver.com</t>
+          <t>nsfitness3@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1443-6318</t>
+          <t>0507-1393-8667</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>광주 남구 봉선2로 49 5층 유산소존 6층 웨이트존</t>
+          <t>광주 남구 서문대로 700 3층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nsfitness5</t>
+          <t>https://nsfitness.imweb.me</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -807,7 +803,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wtveflr</t>
+          <t>https://talk.naver.com/ct/w46fuy</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -817,17 +813,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>374</v>
+        <v>720</v>
       </c>
       <c r="Q4" t="n">
-        <v>587</v>
+        <v>1321</v>
       </c>
       <c r="R4" t="n">
-        <v>961</v>
+        <v>2041</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +832,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1825238671</t>
+          <t>1659855087</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1825238671</t>
+          <t>https://m.place.naver.com/place/1659855087</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -858,29 +854,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>글램핏 상무점 24시 헬스 PT</t>
+          <t>육체미 첨단점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>glamfit23@naver.com</t>
+          <t>abcshowkr@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1348-6107</t>
+          <t>062-972-0002</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>광주 서구 상무중앙로 34 4층</t>
+          <t>광주 광산구 첨단중앙로170번길 92 첨단스포츠센터 5층, 육체미</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/glamfit23</t>
+          <t>https://www.instagram.com/6eauty6ody__chumdan3</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -895,19 +891,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w42a3f</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -919,13 +911,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>351</v>
+        <v>109</v>
       </c>
       <c r="Q5" t="n">
-        <v>1964</v>
+        <v>310</v>
       </c>
       <c r="R5" t="n">
-        <v>2315</v>
+        <v>419</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,17 +926,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1034250827</t>
+          <t>1499021085</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1034250827</t>
+          <t>https://m.place.naver.com/place/1499021085</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1016,10 +1008,10 @@
         <v>412</v>
       </c>
       <c r="Q6" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="R6" t="n">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1038,7 +1030,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1050,34 +1042,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NS휘트니스 선운점</t>
+          <t>���로백피트니스 봉선9호점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nsfitness_seonun@naver.com</t>
+          <t>zeroback2022@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0507-1427-7668</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>광주 광산구 어등대로 555 2동 2층</t>
+          <t>광주 남구 제석로 104 에이치알아팰리스 202동 201호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nsfitness_seonun</t>
+          <t>https://blog.naver.com/zeroback2022/223794738255</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1097,7 +1085,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wh23ln4</t>
+          <t>https://talk.naver.com/ct/w5v90v</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1111,13 +1099,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>73</v>
+        <v>206</v>
       </c>
       <c r="Q7" t="n">
-        <v>116</v>
+        <v>368</v>
       </c>
       <c r="R7" t="n">
-        <v>189</v>
+        <v>574</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,17 +1114,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2097553652</t>
+          <t>1858970955</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2097553652</t>
+          <t>https://m.place.naver.com/place/1858970955</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1148,34 +1136,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>24시 올라운드휘트니스 금호점 헬스 PT</t>
+          <t>24시 헬스 PT 제로백피트니스 첨단점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>allround_fitness5@naver.com</t>
+          <t>zeroback2022@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1438-7908</t>
+          <t>0507-1338-8873</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>광주 서구 운천로 23-1 2~3층</t>
+          <t>광주 광산구 첨단중앙로106번길 29 5층 제로백피트니스</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://allroundfitness.kr</t>
+          <t>https://blog.naver.com/zeroback2022/223794553588</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1195,12 +1183,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wkdxhjp</t>
+          <t>https://talk.naver.com/ct/w5ycoi</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1209,13 +1197,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>266</v>
+        <v>628</v>
       </c>
       <c r="Q8" t="n">
-        <v>636</v>
+        <v>1040</v>
       </c>
       <c r="R8" t="n">
-        <v>902</v>
+        <v>1668</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,17 +1212,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1709345373</t>
+          <t>1862122664</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1709345373</t>
+          <t>https://m.place.naver.com/place/1862122664</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1246,34 +1234,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>24시 올라운드 휘트니스 운암점 헬스 PT</t>
+          <t>NS휘트니스 선운점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>allround_fitness@naver.com</t>
+          <t>nsfitness_seonun@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1461-2096</t>
+          <t>0507-1427-7668</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>광주 북구 북문대로 184 2층</t>
+          <t>광주 광산구 어등대로 555 2동 2층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_GRzxen/chat</t>
+          <t>https://www.instagram.com/nsfitness_seonun</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1293,12 +1281,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/we94hjj</t>
+          <t>https://talk.naver.com/ct/wh23ln4</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1307,13 +1295,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>520</v>
+        <v>77</v>
       </c>
       <c r="Q9" t="n">
-        <v>291</v>
+        <v>119</v>
       </c>
       <c r="R9" t="n">
-        <v>811</v>
+        <v>196</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,17 +1310,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1509126970</t>
+          <t>2097553652</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1509126970</t>
+          <t>https://m.place.naver.com/place/2097553652</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1408,10 +1396,10 @@
         <v>274</v>
       </c>
       <c r="Q10" t="n">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="R10" t="n">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1430,7 +1418,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1503,13 +1491,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q11" t="n">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="R11" t="n">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1528,7 +1516,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/광주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/광주_헬스장.xlsx
@@ -421,12 +421,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="37" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -628,10 +628,10 @@
         <v>645</v>
       </c>
       <c r="Q2" t="n">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="R2" t="n">
-        <v>1105</v>
+        <v>1111</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -854,29 +854,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>육체미 첨단점</t>
+          <t>에스짐24시피트니스 진월점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>abcshowkr@naver.com</t>
+          <t>sgym3@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>062-972-0002</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>광주 광산구 첨단중앙로170번길 92 첨단스포츠센터 5층, 육체미</t>
+          <t>광주 남구 서문대로 665 6층 SGYM 진월점</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/6eauty6ody__chumdan3</t>
+          <t>https://blog.naver.com/sgym3/223208188125</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -891,15 +887,19 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4620r</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -911,13 +911,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>109</v>
+        <v>412</v>
       </c>
       <c r="Q5" t="n">
-        <v>310</v>
+        <v>402</v>
       </c>
       <c r="R5" t="n">
-        <v>419</v>
+        <v>814</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -926,12 +926,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1499021085</t>
+          <t>1264832152</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1499021085</t>
+          <t>https://m.place.naver.com/place/1264832152</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>에스짐24시피트니스 진월점</t>
+          <t>제로백피트니스 봉선9호점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>sgym3@naver.com</t>
+          <t>zeroback2022@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -961,12 +961,12 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>광주 남구 서문대로 665 6층 SGYM 진월점</t>
+          <t>광주 남구 제석로 104 에이치알아팰리스 202동 201호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sgym3/223208188125</t>
+          <t>https://blog.naver.com/zeroback2022/223794738255</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4620r</t>
+          <t>https://talk.naver.com/ct/w5v90v</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1005,13 +1005,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>412</v>
+        <v>206</v>
       </c>
       <c r="Q6" t="n">
-        <v>402</v>
+        <v>368</v>
       </c>
       <c r="R6" t="n">
-        <v>814</v>
+        <v>574</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1264832152</t>
+          <t>1858970955</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1264832152</t>
+          <t>https://m.place.naver.com/place/1858970955</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>���로백피트니스 봉선9호점</t>
+          <t>24시 헬스 PT 제로백피트니스 첨단점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1051,16 +1051,20 @@
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0507-1338-8873</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>광주 남구 제석로 104 에이치알아팰리스 202동 201호</t>
+          <t>광주 광산구 첨단중앙로106번길 29 5층 제로백피트니스</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/zeroback2022/223794738255</t>
+          <t>https://blog.naver.com/zeroback2022/223794553588</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1085,7 +1089,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5v90v</t>
+          <t>https://talk.naver.com/ct/w5ycoi</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1099,13 +1103,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>206</v>
+        <v>628</v>
       </c>
       <c r="Q7" t="n">
-        <v>368</v>
+        <v>1040</v>
       </c>
       <c r="R7" t="n">
-        <v>574</v>
+        <v>1668</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1114,12 +1118,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1858970955</t>
+          <t>1862122664</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1858970955</t>
+          <t>https://m.place.naver.com/place/1862122664</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1136,29 +1140,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>24시 헬스 PT 제로백피트니스 첨단점</t>
+          <t>NS휘트니스 선운점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>zeroback2022@naver.com</t>
+          <t>nsfitness_seonun@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1338-8873</t>
+          <t>0507-1427-7668</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>광주 광산구 첨단중앙로106번길 29 5층 제로백피트니스</t>
+          <t>광주 광산구 어등대로 555 2동 2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/zeroback2022/223794553588</t>
+          <t>https://www.instagram.com/nsfitness_seonun</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1173,7 +1177,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1183,7 +1187,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5ycoi</t>
+          <t>https://talk.naver.com/ct/wh23ln4</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1197,13 +1201,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>628</v>
+        <v>77</v>
       </c>
       <c r="Q8" t="n">
-        <v>1040</v>
+        <v>119</v>
       </c>
       <c r="R8" t="n">
-        <v>1668</v>
+        <v>196</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1212,12 +1216,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1862122664</t>
+          <t>2097553652</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1862122664</t>
+          <t>https://m.place.naver.com/place/2097553652</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1234,34 +1238,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NS휘트니스 선운점</t>
+          <t>24시 올라운드휘트니스 금호점 헬스 PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nsfitness_seonun@naver.com</t>
+          <t>allround_fitness5@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1427-7668</t>
+          <t>0507-1438-7908</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>광주 광산구 어등대로 555 2동 2층</t>
+          <t>광주 서구 운천로 23-1 2~3층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nsfitness_seonun</t>
+          <t>https://allroundfitness.kr</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1271,7 +1275,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1281,12 +1285,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wh23ln4</t>
+          <t>https://talk.naver.com/ct/wkdxhjp</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1295,13 +1299,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>77</v>
+        <v>266</v>
       </c>
       <c r="Q9" t="n">
-        <v>119</v>
+        <v>636</v>
       </c>
       <c r="R9" t="n">
-        <v>196</v>
+        <v>902</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1310,12 +1314,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2097553652</t>
+          <t>1709345373</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2097553652</t>
+          <t>https://m.place.naver.com/place/1709345373</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">

--- a/naver-place-crawler/results_health/광주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/광주_헬스장.xlsx
@@ -421,7 +421,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="Q2" t="n">
         <v>466</v>
       </c>
       <c r="R2" t="n">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>제로백피트니스 봉선9호점</t>
+          <t>24시 헬스 PT 제로백피트니스 첨단점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -957,16 +957,20 @@
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0507-1338-8873</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>광주 남구 제석로 104 에이치알아팰리스 202동 201호</t>
+          <t>광주 광산구 첨단중앙로106번길 29 5층 제로백피트니스</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/zeroback2022/223794738255</t>
+          <t>https://blog.naver.com/zeroback2022/223794553588</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -991,7 +995,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5v90v</t>
+          <t>https://talk.naver.com/ct/w5ycoi</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1005,13 +1009,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>206</v>
+        <v>628</v>
       </c>
       <c r="Q6" t="n">
-        <v>368</v>
+        <v>1040</v>
       </c>
       <c r="R6" t="n">
-        <v>574</v>
+        <v>1668</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1020,12 +1024,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1858970955</t>
+          <t>1862122664</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1858970955</t>
+          <t>https://m.place.naver.com/place/1862122664</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1042,29 +1046,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>24시 헬스 PT 제로백피트니스 첨단점</t>
+          <t>NS휘트니스 선운점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>zeroback2022@naver.com</t>
+          <t>nsfitness_seonun@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1338-8873</t>
+          <t>0507-1427-7668</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>광주 광산구 첨단중앙로106번길 29 5층 제로백피트니스</t>
+          <t>광주 광산구 어등대로 555 2동 2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/zeroback2022/223794553588</t>
+          <t>https://www.instagram.com/nsfitness_seonun</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1079,7 +1083,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1089,7 +1093,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5ycoi</t>
+          <t>https://talk.naver.com/ct/wh23ln4</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1103,13 +1107,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>628</v>
+        <v>80</v>
       </c>
       <c r="Q7" t="n">
-        <v>1040</v>
+        <v>120</v>
       </c>
       <c r="R7" t="n">
-        <v>1668</v>
+        <v>200</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1118,12 +1122,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1862122664</t>
+          <t>2097553652</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1862122664</t>
+          <t>https://m.place.naver.com/place/2097553652</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1140,34 +1144,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NS휘트니스 선운점</t>
+          <t>24시 올라운드휘트니스 금호점 헬스 PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nsfitness_seonun@naver.com</t>
+          <t>allround_fitness5@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1427-7668</t>
+          <t>0507-1438-7908</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>광주 광산구 어등대로 555 2동 2층</t>
+          <t>광주 서구 운천로 23-1 2~3층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nsfitness_seonun</t>
+          <t>https://allroundfitness.kr</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1177,7 +1181,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1187,12 +1191,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wh23ln4</t>
+          <t>https://talk.naver.com/ct/wkdxhjp</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1201,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>77</v>
+        <v>266</v>
       </c>
       <c r="Q8" t="n">
-        <v>119</v>
+        <v>636</v>
       </c>
       <c r="R8" t="n">
-        <v>196</v>
+        <v>902</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1216,12 +1220,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2097553652</t>
+          <t>1709345373</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2097553652</t>
+          <t>https://m.place.naver.com/place/1709345373</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1238,29 +1242,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>24시 올라운드휘트니스 금호점 헬스 PT</t>
+          <t>24시 올라운드 휘트니스 운암점 헬스 PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>allround_fitness5@naver.com</t>
+          <t>allround_fitness@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1438-7908</t>
+          <t>0507-1461-2096</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>광주 서구 운천로 23-1 2~3층</t>
+          <t>광주 북구 북문대로 184 2층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://allroundfitness.kr</t>
+          <t>http://pf.kakao.com/_GRzxen/chat</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1275,7 +1279,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1285,7 +1289,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wkdxhjp</t>
+          <t>https://talk.naver.com/ct/we94hjj</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1299,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>266</v>
+        <v>520</v>
       </c>
       <c r="Q9" t="n">
-        <v>636</v>
+        <v>291</v>
       </c>
       <c r="R9" t="n">
-        <v>902</v>
+        <v>811</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1314,12 +1318,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1709345373</t>
+          <t>1509126970</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1709345373</t>
+          <t>https://m.place.naver.com/place/1509126970</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1336,7 +1340,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>짐플릭스 첨단점</t>
+          <t>짐플릭스 수완점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1347,13 +1351,13 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1364-2795</t>
+          <t>0507-1383-2795</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>광주 광산구 임방울대로800번길 72 3층</t>
+          <t>광주 광산구 임방울대로 342 8층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1397,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="Q10" t="n">
-        <v>850</v>
+        <v>726</v>
       </c>
       <c r="R10" t="n">
-        <v>1124</v>
+        <v>988</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1412,12 +1416,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1955578541</t>
+          <t>1999324427</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1955578541</t>
+          <t>https://m.place.naver.com/place/1999324427</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1434,7 +1438,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>짐플릭스 수완점</t>
+          <t>짐플릭스 첨단점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1445,13 +1449,13 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1383-2795</t>
+          <t>0507-1364-2795</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>광주 광산구 임방울대로 342 8층</t>
+          <t>광주 광산구 임방울대로800번길 72 3층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1495,13 +1499,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="Q11" t="n">
-        <v>726</v>
+        <v>850</v>
       </c>
       <c r="R11" t="n">
-        <v>988</v>
+        <v>1124</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1510,12 +1514,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1999324427</t>
+          <t>1955578541</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1999324427</t>
+          <t>https://m.place.naver.com/place/1955578541</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/광주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/광주_헬스장.xlsx
@@ -427,7 +427,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="37" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="Q2" t="n">
         <v>466</v>
       </c>
       <c r="R2" t="n">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="Q3" t="n">
         <v>701</v>
       </c>
       <c r="R3" t="n">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -820,10 +820,10 @@
         <v>720</v>
       </c>
       <c r="Q4" t="n">
-        <v>1321</v>
+        <v>1325</v>
       </c>
       <c r="R4" t="n">
-        <v>2041</v>
+        <v>2045</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -854,25 +854,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>에스짐24시피트니스 진월점</t>
+          <t>NS휘트니스 선운점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>sgym3@naver.com</t>
+          <t>nsfitness_seonun@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0507-1427-7668</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>광주 남구 서문대로 665 6층 SGYM 진월점</t>
+          <t>광주 광산구 어등대로 555 2동 2층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sgym3/223208188125</t>
+          <t>https://www.instagram.com/nsfitness_seonun</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -887,7 +891,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -897,7 +901,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4620r</t>
+          <t>https://talk.naver.com/ct/wh23ln4</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -911,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>412</v>
+        <v>80</v>
       </c>
       <c r="Q5" t="n">
-        <v>402</v>
+        <v>121</v>
       </c>
       <c r="R5" t="n">
-        <v>814</v>
+        <v>201</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -926,12 +930,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1264832152</t>
+          <t>2097553652</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1264832152</t>
+          <t>https://m.place.naver.com/place/2097553652</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -948,34 +952,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>24시 헬스 PT 제로백피트니스 첨단점</t>
+          <t>24시 올라운드휘트니스 금호점 헬스 PT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>zeroback2022@naver.com</t>
+          <t>allround_fitness5@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1338-8873</t>
+          <t>0507-1438-7908</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>광주 광산구 첨단중앙로106번길 29 5층 제로백피트니스</t>
+          <t>광주 서구 운천로 23-1 2~3층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/zeroback2022/223794553588</t>
+          <t>https://allroundfitness.kr</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -995,12 +999,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5ycoi</t>
+          <t>https://talk.naver.com/ct/wkdxhjp</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1009,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>628</v>
+        <v>266</v>
       </c>
       <c r="Q6" t="n">
-        <v>1040</v>
+        <v>636</v>
       </c>
       <c r="R6" t="n">
-        <v>1668</v>
+        <v>902</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1024,12 +1028,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1862122664</t>
+          <t>1709345373</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1862122664</t>
+          <t>https://m.place.naver.com/place/1709345373</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1046,34 +1050,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NS휘트니스 선운점</t>
+          <t>24시 올라운드 휘트니스 운암점 헬스 PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nsfitness_seonun@naver.com</t>
+          <t>allround_fitness@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1427-7668</t>
+          <t>0507-1461-2096</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>광주 광산구 어등대로 555 2동 2층</t>
+          <t>광주 북구 북문대로 184 2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nsfitness_seonun</t>
+          <t>http://pf.kakao.com/_GRzxen/chat</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1093,12 +1097,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wh23ln4</t>
+          <t>https://talk.naver.com/ct/we94hjj</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1107,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>80</v>
+        <v>520</v>
       </c>
       <c r="Q7" t="n">
-        <v>120</v>
+        <v>291</v>
       </c>
       <c r="R7" t="n">
-        <v>200</v>
+        <v>811</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1122,12 +1126,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2097553652</t>
+          <t>1509126970</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2097553652</t>
+          <t>https://m.place.naver.com/place/1509126970</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1139,39 +1143,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>24시 올라운드휘트니스 금호점 헬스 PT</t>
+          <t>레벨업피트니스 헬스&amp;PT 첨단점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>allround_fitness5@naver.com</t>
+          <t>wjddbqls0383@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1438-7908</t>
+          <t>0507-1317-9336</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>광주 서구 운천로 23-1 2~3층</t>
+          <t>광주 광산구 첨단중앙로124번길 79 2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://allroundfitness.kr</t>
+          <t>https://blog.naver.com/wjddbqls0383</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1186,17 +1190,13 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wkdxhjp</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1205,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>266</v>
+        <v>745</v>
       </c>
       <c r="Q8" t="n">
-        <v>636</v>
+        <v>1081</v>
       </c>
       <c r="R8" t="n">
-        <v>902</v>
+        <v>1826</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1709345373</t>
+          <t>1078877238</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1709345373</t>
+          <t>https://m.place.naver.com/place/1078877238</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1242,34 +1242,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>24시 올라운드 휘트니스 운암점 헬스 PT</t>
+          <t>나우휘트니스 헬스&amp;PT 봉선점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>allround_fitness@naver.com</t>
+          <t>nowfitness_1@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1461-2096</t>
+          <t>0507-1487-8892</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>광주 북구 북문대로 184 2층</t>
+          <t>광주 남구 봉선2로 41 스카이빌딩 3층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_GRzxen/chat</t>
+          <t>https://blog.naver.com/nowfitness_1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/we94hjj</t>
+          <t>https://talk.naver.com/ct/w41axl</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1303,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="Q9" t="n">
-        <v>291</v>
+        <v>252</v>
       </c>
       <c r="R9" t="n">
-        <v>811</v>
+        <v>769</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1509126970</t>
+          <t>1006368175</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1509126970</t>
+          <t>https://m.place.naver.com/place/1006368175</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">

--- a/naver-place-crawler/results_health/광주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/광주_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -427,7 +427,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="37" customWidth="1" min="7" max="7"/>
-    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="37" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>에스짐 헬스PT 용봉점</t>
+          <t>넥스트짐 광주 태전동점 헬스 PT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>sgym14@naver.com</t>
+          <t>applegymblack@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1429-1696</t>
+          <t>0507-1371-0124</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>광주 북구 비엔날레로 80 7층</t>
+          <t>경기 광주시 태봉로 116-18</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sgym14/223917864659</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wejy33f</t>
+          <t>https://talk.naver.com/ct/wv39ze2</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>649</v>
+        <v>729</v>
       </c>
       <c r="Q2" t="n">
-        <v>466</v>
+        <v>942</v>
       </c>
       <c r="R2" t="n">
-        <v>1115</v>
+        <v>1671</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2056986615</t>
+          <t>1303499041</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2056986615</t>
+          <t>https://m.place.naver.com/place/1303499041</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -662,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WE휘트니스 첨단점 헬스 PT 필라테스</t>
+          <t>에스짐 헬스PT 용봉점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>wefit33@naver.com</t>
+          <t>sgym14@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1306-6047</t>
+          <t>0507-1429-1696</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>광주 광산구 임방울대로826번길 29-31 6층 602~608호</t>
+          <t>광주 북구 비엔날레로 80 7층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/wefit_cheomdan</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -704,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wejy33f</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -719,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>517</v>
+        <v>649</v>
       </c>
       <c r="Q3" t="n">
-        <v>701</v>
+        <v>472</v>
       </c>
       <c r="R3" t="n">
-        <v>1218</v>
+        <v>1121</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,17 +738,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1094731490</t>
+          <t>2056986615</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1094731490</t>
+          <t>https://m.place.naver.com/place/2056986615</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -756,56 +760,52 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NS휘트니스 진월점 헬스장 PT</t>
+          <t>WE휘트니스 첨단점 헬스 PT 필라테스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nsfitness3@naver.com</t>
+          <t>wefit33@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1393-8667</t>
+          <t>0507-1306-6047</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>광주 남구 서문대로 700 3층</t>
+          <t>광주 광산구 임방울대로826번길 29-31 6층 602~608호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://nsfitness.imweb.me</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w46fuy</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>720</v>
+        <v>517</v>
       </c>
       <c r="Q4" t="n">
-        <v>1325</v>
+        <v>701</v>
       </c>
       <c r="R4" t="n">
-        <v>2045</v>
+        <v>1218</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,17 +832,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1659855087</t>
+          <t>1094731490</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1659855087</t>
+          <t>https://m.place.naver.com/place/1094731490</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -854,34 +854,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NS휘트니스 선운점</t>
+          <t>NS휘트니스 진월점 헬스장 PT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nsfitness_seonun@naver.com</t>
+          <t>nsfitness3@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1427-7668</t>
+          <t>0507-1393-8667</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>광주 광산구 어등대로 555 2동 2층</t>
+          <t>광주 남구 서문대로 700 3층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nsfitness_seonun</t>
+          <t>https://nsfitness.imweb.me</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wh23ln4</t>
+          <t>https://talk.naver.com/ct/w46fuy</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>80</v>
+        <v>720</v>
       </c>
       <c r="Q5" t="n">
-        <v>121</v>
+        <v>1325</v>
       </c>
       <c r="R5" t="n">
-        <v>201</v>
+        <v>2045</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,17 +930,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2097553652</t>
+          <t>1659855087</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2097553652</t>
+          <t>https://m.place.naver.com/place/1659855087</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -952,44 +952,40 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>24시 올라운드휘트니스 금호점 헬스 PT</t>
+          <t>에스짐24시피트니스 진월점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>allround_fitness5@naver.com</t>
+          <t>sgym3@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0507-1438-7908</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>광주 서구 운천로 23-1 2~3층</t>
+          <t>광주 남구 서문대로 665 6층 SGYM 진월점</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://allroundfitness.kr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -999,12 +995,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wkdxhjp</t>
+          <t>https://talk.naver.com/ct/w4620r</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1013,13 +1009,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>266</v>
+        <v>411</v>
       </c>
       <c r="Q6" t="n">
-        <v>636</v>
+        <v>402</v>
       </c>
       <c r="R6" t="n">
-        <v>902</v>
+        <v>813</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,17 +1024,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1709345373</t>
+          <t>1264832152</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1709345373</t>
+          <t>https://m.place.naver.com/place/1264832152</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1050,29 +1046,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>24시 올라운드 휘트니스 운암점 헬스 PT</t>
+          <t>24시 올라운드휘트니스 금호점 헬스 PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>allround_fitness@naver.com</t>
+          <t>allround_fitness5@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1461-2096</t>
+          <t>0507-1438-7908</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>광주 북구 북문대로 184 2층</t>
+          <t>광주 서구 운천로 23-1 2~3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_GRzxen/chat</t>
+          <t>https://allroundfitness.kr</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1087,7 +1083,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1097,7 +1093,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/we94hjj</t>
+          <t>https://talk.naver.com/ct/wkdxhjp</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1111,13 +1107,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>520</v>
+        <v>266</v>
       </c>
       <c r="Q7" t="n">
-        <v>291</v>
+        <v>636</v>
       </c>
       <c r="R7" t="n">
-        <v>811</v>
+        <v>902</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,51 +1122,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1509126970</t>
+          <t>1709345373</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1509126970</t>
+          <t>https://m.place.naver.com/place/1709345373</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>레벨업피트니스 헬스&amp;PT 첨단점</t>
+          <t>24시 올라운드 휘트니스 운암점 헬스 PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>wjddbqls0383@naver.com</t>
+          <t>allround_fitness@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1317-9336</t>
+          <t>0507-1461-2096</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>광주 광산구 첨단중앙로124번길 79 2층</t>
+          <t>광주 북구 북문대로 184 2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wjddbqls0383</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1180,23 +1176,27 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/we94hjj</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1205,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>745</v>
+        <v>520</v>
       </c>
       <c r="Q8" t="n">
-        <v>1081</v>
+        <v>291</v>
       </c>
       <c r="R8" t="n">
-        <v>1826</v>
+        <v>811</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,51 +1220,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1078877238</t>
+          <t>1509126970</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1078877238</t>
+          <t>https://m.place.naver.com/place/1509126970</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>나우휘트니스 헬스&amp;PT 봉선점</t>
+          <t>레벨업피트니스 헬스&amp;PT 첨단점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nowfitness_1@naver.com</t>
+          <t>wjddbqls0383@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1487-8892</t>
+          <t>0507-1317-9336</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>광주 남구 봉선2로 41 스카이빌딩 3층</t>
+          <t>광주 광산구 첨단중앙로124번길 79 2층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nowfitness_1</t>
+          <t>https://blog.naver.com/wjddbqls0383</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1284,14 +1284,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w41axl</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1303,13 +1299,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>517</v>
+        <v>745</v>
       </c>
       <c r="Q9" t="n">
-        <v>252</v>
+        <v>1081</v>
       </c>
       <c r="R9" t="n">
-        <v>769</v>
+        <v>1826</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,61 +1314,61 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1006368175</t>
+          <t>1078877238</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1006368175</t>
+          <t>https://m.place.naver.com/place/1078877238</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>짐플릭스 수완점</t>
+          <t>올타임피트니스 조선대 2호점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>gymflix@naver.com</t>
+          <t>xzasdr00@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1383-2795</t>
+          <t>0507-1323-2431</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>광주 광산구 임방울대로 342 8층</t>
+          <t>광주 동구 지산로 3 2,3층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.gymflix.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1382,14 +1378,10 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wkfba0h</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1397,17 +1389,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>262</v>
+        <v>10</v>
       </c>
       <c r="Q10" t="n">
-        <v>726</v>
+        <v>12</v>
       </c>
       <c r="R10" t="n">
-        <v>988</v>
+        <v>22</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,17 +1408,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1999324427</t>
+          <t>2094473102</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1999324427</t>
+          <t>https://m.place.naver.com/place/2094473102</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1438,7 +1430,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>짐플릭스 첨단점</t>
+          <t>짐플릭스 수완점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1449,82 +1441,180 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1364-2795</t>
+          <t>0507-1383-2795</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
+          <t>광주 광산구 임방울대로 342 8층</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://www.gymflix.co.kr/</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wkfba0h</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>262</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>726</v>
+      </c>
+      <c r="R11" t="n">
+        <v>988</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1999324427</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1999324427</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>짐플릭스 첨단점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>gymflix@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1364-2795</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>광주 광산구 임방울대로800번길 72 3층</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>https://www.gymflix.co.kr/</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>https://talk.naver.com/ct/wkfba0h</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
         <v>274</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q12" t="n">
         <v>850</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R12" t="n">
         <v>1124</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>1955578541</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1955578541</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/광주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/광주_헬스장.xlsx
@@ -427,7 +427,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="37" customWidth="1" min="7" max="7"/>
-    <col width="37" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -569,7 +569,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>applegymblack@naver.com</t>
+          <t>nextgym07@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -586,7 +586,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/nextgym07</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/sgym14/223917864659</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,12 +694,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -726,10 +726,10 @@
         <v>649</v>
       </c>
       <c r="Q3" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="R3" t="n">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/wefit_cheomdan</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/sgym3/223208188125</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -980,12 +980,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>24시 올라운드휘트니스 금호점 헬스 PT</t>
+          <t>NS휘트니스 선운점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>allround_fitness5@naver.com</t>
+          <t>nsfitness_seonun@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1438-7908</t>
+          <t>0507-1427-7668</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>광주 서구 운천로 23-1 2~3층</t>
+          <t>광주 광산구 어등대로 555 2동 2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://allroundfitness.kr</t>
+          <t>https://www.instagram.com/nsfitness_seonun</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1093,12 +1093,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wkdxhjp</t>
+          <t>https://talk.naver.com/ct/wh23ln4</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1107,13 +1107,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>266</v>
+        <v>80</v>
       </c>
       <c r="Q7" t="n">
-        <v>636</v>
+        <v>121</v>
       </c>
       <c r="R7" t="n">
-        <v>902</v>
+        <v>201</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1709345373</t>
+          <t>2097553652</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1709345373</t>
+          <t>https://m.place.naver.com/place/2097553652</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1144,44 +1144,44 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>24시 올라운드 휘트니스 운암점 헬스 PT</t>
+          <t>24시 올라운드휘트니스 금호점 헬스 PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>allround_fitness@naver.com</t>
+          <t>allround_fitness5@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1461-2096</t>
+          <t>0507-1438-7908</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>광주 북구 북문대로 184 2층</t>
+          <t>광주 서구 운천로 23-1 2~3층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://allroundfitness.kr</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/we94hjj</t>
+          <t>https://talk.naver.com/ct/wkdxhjp</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1205,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>520</v>
+        <v>266</v>
       </c>
       <c r="Q8" t="n">
-        <v>291</v>
+        <v>636</v>
       </c>
       <c r="R8" t="n">
-        <v>811</v>
+        <v>902</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1509126970</t>
+          <t>1709345373</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1509126970</t>
+          <t>https://m.place.naver.com/place/1709345373</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1237,39 +1237,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>레벨업피트니스 헬스&amp;PT 첨단점</t>
+          <t>24시 올라운드 휘트니스 운암점 헬스 PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>wjddbqls0383@naver.com</t>
+          <t>allround_fitness@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1317-9336</t>
+          <t>0507-1461-2096</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>광주 광산구 첨단중앙로124번길 79 2층</t>
+          <t>광주 북구 북문대로 184 2층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wjddbqls0383</t>
+          <t>http://pf.kakao.com/_GRzxen/chat</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1279,18 +1279,22 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/we94hjj</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1299,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>745</v>
+        <v>520</v>
       </c>
       <c r="Q9" t="n">
-        <v>1081</v>
+        <v>291</v>
       </c>
       <c r="R9" t="n">
-        <v>1826</v>
+        <v>811</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1314,12 +1318,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1078877238</t>
+          <t>1509126970</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1078877238</t>
+          <t>https://m.place.naver.com/place/1509126970</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1331,34 +1335,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>올타임피트니스 조선대 2호점</t>
+          <t>레벨업피트니스 헬스&amp;PT 첨단점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>xzasdr00@naver.com</t>
+          <t>wjddbqls0383@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1323-2431</t>
+          <t>0507-1317-9336</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>광주 동구 지산로 3 2,3층</t>
+          <t>광주 광산구 첨단중앙로124번길 79 2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/wjddbqls0383</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1368,12 +1372,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1389,17 +1393,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>10</v>
+        <v>745</v>
       </c>
       <c r="Q10" t="n">
-        <v>12</v>
+        <v>1081</v>
       </c>
       <c r="R10" t="n">
-        <v>22</v>
+        <v>1826</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1408,12 +1412,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2094473102</t>
+          <t>1078877238</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2094473102</t>
+          <t>https://m.place.naver.com/place/1078877238</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">

--- a/naver-place-crawler/results_health/광주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/광주_헬스장.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="37" customWidth="1" min="7" max="7"/>
-    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>에스짐 헬스PT 용봉점</t>
+          <t>넥스트짐 광주 태전동점 헬스 PT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>sgym14@naver.com</t>
+          <t>nextgym07@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1429-1696</t>
+          <t>0507-1371-0124</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>광주 북구 비엔날레로 80 7층</t>
+          <t>경기 광주시 태봉로 116-18</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sgym14/223917864659</t>
+          <t>https://blog.naver.com/nextgym07</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wejy33f</t>
+          <t>https://talk.naver.com/ct/wv39ze2</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>649</v>
+        <v>730</v>
       </c>
       <c r="Q2" t="n">
-        <v>474</v>
+        <v>944</v>
       </c>
       <c r="R2" t="n">
-        <v>1123</v>
+        <v>1674</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2056986615</t>
+          <t>1303499041</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2056986615</t>
+          <t>https://m.place.naver.com/place/1303499041</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -662,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WE휘트니스 첨단점 헬스 PT 필라테스</t>
+          <t>에스짐 헬스PT 용봉점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>wefit33@naver.com</t>
+          <t>sgym14@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1306-6047</t>
+          <t>0507-1429-1696</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>광주 광산구 임방울대로826번길 29-31 6층 602~608호</t>
+          <t>광주 북구 비엔날레로 80 7층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/wefit_cheomdan</t>
+          <t>https://blog.naver.com/sgym14/223917864659</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -699,15 +699,19 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wejy33f</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -719,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>518</v>
+        <v>650</v>
       </c>
       <c r="Q3" t="n">
-        <v>701</v>
+        <v>476</v>
       </c>
       <c r="R3" t="n">
-        <v>1219</v>
+        <v>1126</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1094731490</t>
+          <t>2056986615</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1094731490</t>
+          <t>https://m.place.naver.com/place/2056986615</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -756,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NS휘트니스 진월점 헬스장 PT</t>
+          <t>WE휘트니스 첨단점 헬스 PT 필라테스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nsfitness3@naver.com</t>
+          <t>wefit33@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1393-8667</t>
+          <t>0507-1306-6047</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>광주 남구 서문대로 700 3층</t>
+          <t>광주 광산구 임방울대로826번길 29-31 6층 602~608호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://nsfitness.imweb.me</t>
+          <t>https://www.instagram.com/wefit_cheomdan</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -793,19 +797,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w46fuy</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>721</v>
+        <v>519</v>
       </c>
       <c r="Q4" t="n">
-        <v>1330</v>
+        <v>702</v>
       </c>
       <c r="R4" t="n">
-        <v>2051</v>
+        <v>1221</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,12 +832,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1659855087</t>
+          <t>1094731490</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1659855087</t>
+          <t>https://m.place.naver.com/place/1094731490</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -854,30 +854,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>에스짐24시피트니스 진월점</t>
+          <t>NS휘트니스 진월점 헬스장 PT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>sgym3@naver.com</t>
+          <t>nsfitness3@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0507-1393-8667</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>광주 남구 서문대로 665 6층 SGYM 진월점</t>
+          <t>광주 남구 서문대로 700 3층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sgym3/223208188125</t>
+          <t>https://nsfitness.imweb.me</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -897,7 +901,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4620r</t>
+          <t>https://talk.naver.com/ct/w46fuy</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -911,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>411</v>
+        <v>721</v>
       </c>
       <c r="Q5" t="n">
-        <v>401</v>
+        <v>1334</v>
       </c>
       <c r="R5" t="n">
-        <v>812</v>
+        <v>2055</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -926,12 +930,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1264832152</t>
+          <t>1659855087</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1264832152</t>
+          <t>https://m.place.naver.com/place/1659855087</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -948,29 +952,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>24시 올라운드휘트니스 금호점 헬스 PT</t>
+          <t>에스짐24시피트니스 진월점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>allround_fitness5@naver.com</t>
+          <t>sgym3@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0507-1438-7908</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>광주 서구 운천로 23-1 2~3층</t>
+          <t>광주 남구 서문대로 665 6층 SGYM 진월점</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://allroundfitness.kr</t>
+          <t>https://blog.naver.com/sgym3/223208188125</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -995,12 +995,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wkdxhjp</t>
+          <t>https://talk.naver.com/ct/w4620r</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1009,13 +1009,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>267</v>
+        <v>411</v>
       </c>
       <c r="Q6" t="n">
-        <v>637</v>
+        <v>401</v>
       </c>
       <c r="R6" t="n">
-        <v>904</v>
+        <v>812</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1709345373</t>
+          <t>1264832152</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1709345373</t>
+          <t>https://m.place.naver.com/place/1264832152</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1046,12 +1046,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>일그램휘트니스 필라테스 헬스 PT 연중무휴</t>
+          <t>제로백피트니스 봉선9호점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1gramfitness@naver.com</t>
+          <t>zeroback2022@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -1059,12 +1059,12 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>광주 북구 대자로 36 MVG빌딩 4층 일그램휘트니스&amp;필라테스</t>
+          <t>광주 남구 제석로 104 에이치알아팰리스 202동 201호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/1gramfitness</t>
+          <t>https://blog.naver.com/zeroback2022/223794738255</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w48i0v</t>
+          <t>https://talk.naver.com/ct/w5v90v</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1103,13 +1103,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>154</v>
+        <v>206</v>
       </c>
       <c r="Q7" t="n">
-        <v>299</v>
+        <v>368</v>
       </c>
       <c r="R7" t="n">
-        <v>453</v>
+        <v>574</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1943126446</t>
+          <t>1858970955</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1943126446</t>
+          <t>https://m.place.naver.com/place/1858970955</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1140,29 +1140,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>에스짐24시 헬스피티 오치점</t>
+          <t>24시 헬스 PT 제로백피트니스 상무지구점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>sgym7@naver.com</t>
+          <t>zeroback2022@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1447-1008</t>
+          <t>0507-1490-0243</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>광주 북구 설죽로 333 3층 에스짐 오치점</t>
+          <t>광주 서구 상무중앙로 7 8층 802호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sgym7/224050853237</t>
+          <t>https://blog.naver.com/zeroback2022/223830063211</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5xlgd</t>
+          <t>https://talk.naver.com/ct/w5yb72</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1197,17 +1197,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>334</v>
+        <v>316</v>
       </c>
       <c r="Q8" t="n">
-        <v>289</v>
+        <v>614</v>
       </c>
       <c r="R8" t="n">
-        <v>623</v>
+        <v>930</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1103489963</t>
+          <t>1013874419</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1103489963</t>
+          <t>https://m.place.naver.com/place/1013874419</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1233,39 +1233,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>짐플릭스 수완점</t>
+          <t>24시 헬스 PT 제로백피트니스 첨단점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>gymflix@naver.com</t>
+          <t>zeroback2022@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1383-2795</t>
+          <t>0507-1338-8873</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>광주 광산구 임방울대로 342 8층</t>
+          <t>광주 광산구 첨단중앙로106번길 29 5층 제로백피트니스</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.gymflix.co.kr/</t>
+          <t>https://blog.naver.com/zeroback2022/223794553588</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wkfba0h</t>
+          <t>https://talk.naver.com/ct/w5ycoi</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>262</v>
+        <v>628</v>
       </c>
       <c r="Q9" t="n">
-        <v>726</v>
+        <v>1043</v>
       </c>
       <c r="R9" t="n">
-        <v>988</v>
+        <v>1671</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1314,12 +1314,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1999324427</t>
+          <t>1862122664</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1999324427</t>
+          <t>https://m.place.naver.com/place/1862122664</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1331,39 +1331,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>짐플릭스 첨단점</t>
+          <t>NS휘트니스 선운점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>gymflix@naver.com</t>
+          <t>nsfitness_seonun@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1364-2795</t>
+          <t>0507-1427-7668</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>광주 광산구 임방울대로800번길 72 3층</t>
+          <t>광주 광산구 어등대로 555 2동 2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.gymflix.co.kr/</t>
+          <t>https://www.instagram.com/nsfitness_seonun</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wkfba0h</t>
+          <t>https://talk.naver.com/ct/wh23ln4</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1397,13 +1397,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>274</v>
+        <v>81</v>
       </c>
       <c r="Q10" t="n">
-        <v>850</v>
+        <v>123</v>
       </c>
       <c r="R10" t="n">
-        <v>1124</v>
+        <v>204</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1955578541</t>
+          <t>2097553652</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1955578541</t>
+          <t>https://m.place.naver.com/place/2097553652</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1429,39 +1429,39 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>모모필라테스 상무점</t>
+          <t>짐플릭스 수완점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>horror3988@naver.com</t>
+          <t>gymflix@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1381-5321</t>
+          <t>0507-1383-2795</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>광주 서구 치평로 60 4층 406호</t>
+          <t>광주 광산구 임방울대로 342 8층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/horror3988</t>
+          <t>https://www.gymflix.co.kr/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w44ao6</t>
+          <t>https://talk.naver.com/ct/wkfba0h</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1495,13 +1495,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>157</v>
+        <v>262</v>
       </c>
       <c r="Q11" t="n">
-        <v>160</v>
+        <v>723</v>
       </c>
       <c r="R11" t="n">
-        <v>317</v>
+        <v>985</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1510,15 +1510,113 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1555723762</t>
+          <t>1999324427</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1555723762</t>
+          <t>https://m.place.naver.com/place/1999324427</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>짐플릭스 첨단점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>gymflix@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1364-2795</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>광주 광산구 임방울대로800번길 72 3층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.gymflix.co.kr/</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wkfba0h</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>275</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>847</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1122</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1955578541</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1955578541</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-28</t>
         </is>

--- a/naver-place-crawler/results_health/광주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/광주_헬스장.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="37" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -918,10 +918,10 @@
         <v>721</v>
       </c>
       <c r="Q5" t="n">
-        <v>1334</v>
+        <v>1336</v>
       </c>
       <c r="R5" t="n">
-        <v>2055</v>
+        <v>2057</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -952,30 +952,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>에스짐24시피트니스 진월점</t>
+          <t>24시 올라운드휘트니스 금호점 헬스 PT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>sgym3@naver.com</t>
+          <t>allround_fitness5@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0507-1438-7908</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>광주 남구 서문대로 665 6층 SGYM 진월점</t>
+          <t>광주 서구 운천로 23-1 2~3층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sgym3/223208188125</t>
+          <t>https://allroundfitness.kr</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -995,12 +999,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4620r</t>
+          <t>https://talk.naver.com/ct/wkdxhjp</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1009,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>411</v>
+        <v>267</v>
       </c>
       <c r="Q6" t="n">
-        <v>401</v>
+        <v>639</v>
       </c>
       <c r="R6" t="n">
-        <v>812</v>
+        <v>906</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1024,17 +1028,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1264832152</t>
+          <t>1709345373</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1264832152</t>
+          <t>https://m.place.naver.com/place/1709345373</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1046,30 +1050,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>제로백피트니스 봉선9호점</t>
+          <t>24시 올라운드 휘트니스 운암점 헬스 PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>zeroback2022@naver.com</t>
+          <t>allround_fitness@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0507-1461-2096</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>광주 남구 제석로 104 에이치알아팰리스 202동 201호</t>
+          <t>광주 북구 북문대로 184 2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/zeroback2022/223794738255</t>
+          <t>http://pf.kakao.com/_GRzxen/chat</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1079,7 +1087,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1089,12 +1097,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5v90v</t>
+          <t>https://talk.naver.com/ct/we94hjj</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1103,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>206</v>
+        <v>521</v>
       </c>
       <c r="Q7" t="n">
-        <v>368</v>
+        <v>291</v>
       </c>
       <c r="R7" t="n">
-        <v>574</v>
+        <v>812</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1118,51 +1126,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1858970955</t>
+          <t>1509126970</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1858970955</t>
+          <t>https://m.place.naver.com/place/1509126970</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>24시 헬스 PT 제로백피트니스 상무지구점</t>
+          <t>레벨업피트니스 헬스&amp;PT 첨단점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>zeroback2022@naver.com</t>
+          <t>wjddbqls0383@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1490-0243</t>
+          <t>0507-1317-9336</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>광주 서구 상무중앙로 7 8층 802호</t>
+          <t>광주 광산구 첨단중앙로124번길 79 2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/zeroback2022/223830063211</t>
+          <t>https://blog.naver.com/wjddbqls0383</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1182,14 +1190,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5yb72</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1197,17 +1201,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>316</v>
+        <v>747</v>
       </c>
       <c r="Q8" t="n">
-        <v>614</v>
+        <v>1081</v>
       </c>
       <c r="R8" t="n">
-        <v>930</v>
+        <v>1828</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1216,17 +1220,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1013874419</t>
+          <t>1078877238</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1013874419</t>
+          <t>https://m.place.naver.com/place/1078877238</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1238,29 +1242,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>24시 헬스 PT 제로백피트니스 첨단점</t>
+          <t>에스짐24시 헬스피티 오치점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>zeroback2022@naver.com</t>
+          <t>sgym7@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1338-8873</t>
+          <t>0507-1447-1008</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>광주 광산구 첨단중앙로106번길 29 5층 제로백피트니스</t>
+          <t>광주 북구 설죽로 333 3층 에스짐 오치점</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/zeroback2022/223794553588</t>
+          <t>https://blog.naver.com/sgym7/224050853237</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1285,7 +1289,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5ycoi</t>
+          <t>https://talk.naver.com/ct/w5xlgd</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1299,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>628</v>
+        <v>334</v>
       </c>
       <c r="Q9" t="n">
-        <v>1043</v>
+        <v>289</v>
       </c>
       <c r="R9" t="n">
-        <v>1671</v>
+        <v>623</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1314,56 +1318,56 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1862122664</t>
+          <t>1103489963</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1862122664</t>
+          <t>https://m.place.naver.com/place/1103489963</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NS휘트니스 선운점</t>
+          <t>짐플릭스 수완점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>nsfitness_seonun@naver.com</t>
+          <t>gymflix@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1427-7668</t>
+          <t>0507-1383-2795</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>광주 광산구 어등대로 555 2동 2층</t>
+          <t>광주 광산구 임방울대로 342 8층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nsfitness_seonun</t>
+          <t>https://www.gymflix.co.kr/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1383,7 +1387,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wh23ln4</t>
+          <t>https://talk.naver.com/ct/wkfba0h</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1397,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>81</v>
+        <v>262</v>
       </c>
       <c r="Q10" t="n">
-        <v>123</v>
+        <v>723</v>
       </c>
       <c r="R10" t="n">
-        <v>204</v>
+        <v>985</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1412,17 +1416,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2097553652</t>
+          <t>1999324427</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2097553652</t>
+          <t>https://m.place.naver.com/place/1999324427</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1438,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>짐플릭스 수완점</t>
+          <t>짐플릭스 첨단점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1445,13 +1449,13 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1383-2795</t>
+          <t>0507-1364-2795</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>광주 광산구 임방울대로 342 8층</t>
+          <t>광주 광산구 임방울대로800번길 72 3층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1495,13 +1499,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="Q11" t="n">
-        <v>723</v>
+        <v>847</v>
       </c>
       <c r="R11" t="n">
-        <v>985</v>
+        <v>1122</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1510,115 +1514,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1999324427</t>
+          <t>1955578541</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1999324427</t>
+          <t>https://m.place.naver.com/place/1955578541</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>짐플릭스 첨단점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>gymflix@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1364-2795</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>광주 광산구 임방울대로800번길 72 3층</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://www.gymflix.co.kr/</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wkfba0h</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>275</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>847</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1122</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1955578541</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1955578541</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/광주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/광주_헬스장.xlsx
@@ -726,10 +726,10 @@
         <v>650</v>
       </c>
       <c r="Q3" t="n">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="R3" t="n">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -918,10 +918,10 @@
         <v>721</v>
       </c>
       <c r="Q5" t="n">
-        <v>1336</v>
+        <v>1338</v>
       </c>
       <c r="R5" t="n">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -952,34 +952,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>24시 올라운드휘트니스 금호점 헬스 PT</t>
+          <t>에스짐24시피트니스 진월점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>allround_fitness5@naver.com</t>
+          <t>sgym3@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0507-1438-7908</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>광주 서구 운천로 23-1 2~3층</t>
+          <t>광주 남구 서문대로 665 6층 SGYM 진월점</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://allroundfitness.kr</t>
+          <t>https://blog.naver.com/sgym3/223208188125</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -999,12 +995,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wkdxhjp</t>
+          <t>https://talk.naver.com/ct/w4620r</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1013,13 +1009,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>267</v>
+        <v>411</v>
       </c>
       <c r="Q6" t="n">
-        <v>639</v>
+        <v>401</v>
       </c>
       <c r="R6" t="n">
-        <v>906</v>
+        <v>812</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,12 +1024,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1709345373</t>
+          <t>1264832152</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1709345373</t>
+          <t>https://m.place.naver.com/place/1264832152</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1050,29 +1046,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>24시 올라운드 휘트니스 운암점 헬스 PT</t>
+          <t>24시 올라운드휘트니스 금호점 헬스 PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>allround_fitness@naver.com</t>
+          <t>allround_fitness5@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1461-2096</t>
+          <t>0507-1438-7908</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>광주 북구 북문대로 184 2층</t>
+          <t>광주 서구 운천로 23-1 2~3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_GRzxen/chat</t>
+          <t>https://allroundfitness.kr</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1087,7 +1083,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1097,7 +1093,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/we94hjj</t>
+          <t>https://talk.naver.com/ct/wkdxhjp</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1111,13 +1107,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>521</v>
+        <v>267</v>
       </c>
       <c r="Q7" t="n">
-        <v>291</v>
+        <v>639</v>
       </c>
       <c r="R7" t="n">
-        <v>812</v>
+        <v>906</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,12 +1122,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1509126970</t>
+          <t>1709345373</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1509126970</t>
+          <t>https://m.place.naver.com/place/1709345373</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1143,39 +1139,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>레벨업피트니스 헬스&amp;PT 첨단점</t>
+          <t>24시 올라운드 휘트니스 운암점 헬스 PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>wjddbqls0383@naver.com</t>
+          <t>allround_fitness@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1317-9336</t>
+          <t>0507-1461-2096</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>광주 광산구 첨단중앙로124번길 79 2층</t>
+          <t>광주 북구 북문대로 184 2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wjddbqls0383</t>
+          <t>http://pf.kakao.com/_GRzxen/chat</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1185,18 +1181,22 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/we94hjj</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1205,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>747</v>
+        <v>521</v>
       </c>
       <c r="Q8" t="n">
-        <v>1081</v>
+        <v>291</v>
       </c>
       <c r="R8" t="n">
-        <v>1828</v>
+        <v>812</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1078877238</t>
+          <t>1509126970</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1078877238</t>
+          <t>https://m.place.naver.com/place/1509126970</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
